--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-ai-performance-metrics.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-ai-performance-metrics.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="148">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,11 +283,21 @@
     <t>Extension.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -310,6 +320,9 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>Extension.extension:metric.id</t>
@@ -783,7 +796,7 @@
     <col min="1" max="1" width="43.59375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.1796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.26953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -1146,11 +1159,11 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>75</v>
@@ -1165,15 +1178,17 @@
         <v>18</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>18</v>
@@ -1210,19 +1225,19 @@
         <v>18</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
@@ -1237,31 +1252,31 @@
         <v>77</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -1270,13 +1285,13 @@
         <v>18</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1327,7 +1342,7 @@
         <v>18</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1347,10 +1362,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1450,10 +1465,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1461,7 +1476,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>75</v>
@@ -1476,13 +1491,13 @@
         <v>18</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1521,19 +1536,19 @@
         <v>18</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1551,15 +1566,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>18</v>
@@ -1572,7 +1587,7 @@
         <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -1581,13 +1596,13 @@
         <v>18</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1638,7 +1653,7 @@
         <v>18</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1658,10 +1673,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1761,10 +1776,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1787,13 +1802,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1832,19 +1847,19 @@
         <v>18</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1864,10 +1879,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1890,16 +1905,16 @@
         <v>18</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -1907,7 +1922,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>18</v>
@@ -1949,7 +1964,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -1964,15 +1979,15 @@
         <v>18</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1995,13 +2010,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2028,11 +2043,11 @@
         <v>18</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>18</v>
@@ -2050,7 +2065,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2059,24 +2074,24 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>18</v>
@@ -2089,7 +2104,7 @@
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -2098,13 +2113,13 @@
         <v>18</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2155,7 +2170,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2175,10 +2190,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2278,10 +2293,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2304,13 +2319,13 @@
         <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2349,19 +2364,19 @@
         <v>18</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2381,10 +2396,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2407,16 +2422,16 @@
         <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2424,7 +2439,7 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>18</v>
@@ -2466,7 +2481,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2481,15 +2496,15 @@
         <v>18</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2512,13 +2527,13 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2569,7 +2584,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2578,21 +2593,21 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2615,16 +2630,16 @@
         <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2632,7 +2647,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>18</v>
@@ -2674,7 +2689,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2689,15 +2704,15 @@
         <v>18</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2720,13 +2735,13 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2777,7 +2792,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2786,24 +2801,24 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>18</v>
@@ -2816,7 +2831,7 @@
         <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -2825,13 +2840,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2882,7 +2897,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2902,10 +2917,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3005,10 +3020,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3031,13 +3046,13 @@
         <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3076,19 +3091,19 @@
         <v>18</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3108,10 +3123,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3134,16 +3149,16 @@
         <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3151,7 +3166,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>18</v>
@@ -3193,7 +3208,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3208,15 +3223,15 @@
         <v>18</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3239,13 +3254,13 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3296,7 +3311,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3305,21 +3320,21 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3342,16 +3357,16 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3401,7 +3416,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3416,15 +3431,15 @@
         <v>18</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3447,13 +3462,13 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3504,7 +3519,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3513,13 +3528,13 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
